--- a/database/seeders/excel/type.xlsx
+++ b/database/seeders/excel/type.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC98BEE5-D6E3-4EE7-89A9-A56E475A9BE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF61E3D-13D3-402A-BBFD-FCA05090980C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>id</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>Tidak Diketahui</t>
+  </si>
+  <si>
+    <t>Smartphone</t>
   </si>
 </sst>
 </file>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -441,9 +444,17 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>99</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
     </row>
